--- a/feri-alb-toolkit/feri/example_dataset.xlsx
+++ b/feri-alb-toolkit/feri/example_dataset.xlsx
@@ -478,7 +478,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -486,16 +486,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>185.88</v>
+        <v>33.545</v>
       </c>
       <c r="E3" t="n">
-        <v>4.888644</v>
+        <v>0.9148759999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -503,7 +503,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.12</v>
+        <v>37.44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08017200000000001</v>
+        <v>0.7368</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="E5" t="n">
-        <v>1.578</v>
+        <v>0.0873</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48.26</v>
+        <v>21.24</v>
       </c>
       <c r="E6" t="n">
-        <v>0.632206</v>
+        <v>0.5927397499999999</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.04</v>
+        <v>33.761</v>
       </c>
       <c r="E7" t="n">
-        <v>1.316052</v>
+        <v>0.233704</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -603,7 +603,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>33.545</v>
+        <v>27.965</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9148759999999999</v>
+        <v>0.336256</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -628,7 +628,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -636,16 +636,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37.44</v>
+        <v>7.2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7368</v>
+        <v>0.220056</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -653,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -661,16 +661,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33.3</v>
+        <v>40.61499999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0873</v>
+        <v>0.61803575</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -678,7 +678,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.24</v>
+        <v>36.446</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5927397499999999</v>
+        <v>0.54683575</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -703,7 +703,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>33.761</v>
+        <v>24.163</v>
       </c>
       <c r="E12" t="n">
-        <v>0.233704</v>
+        <v>0.54683575</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -728,7 +728,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.965</v>
+        <v>44.726</v>
       </c>
       <c r="E13" t="n">
-        <v>0.336256</v>
+        <v>0.67883575</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.2</v>
+        <v>39.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.220056</v>
+        <v>1.165008</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40.61499999999999</v>
+        <v>23.292</v>
       </c>
       <c r="E15" t="n">
-        <v>0.61803575</v>
+        <v>0.287056</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -803,7 +803,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>36.446</v>
+        <v>24.703</v>
       </c>
       <c r="E16" t="n">
-        <v>0.54683575</v>
+        <v>0.404152</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>24.163</v>
+        <v>25.063</v>
       </c>
       <c r="E17" t="n">
-        <v>0.54683575</v>
+        <v>0.503656</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -853,7 +853,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>44.726</v>
+        <v>22.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.67883575</v>
+        <v>0.335604</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39.6</v>
+        <v>5.94</v>
       </c>
       <c r="E19" t="n">
-        <v>1.165008</v>
+        <v>0.21713175</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -903,7 +903,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>23.292</v>
+        <v>27.763</v>
       </c>
       <c r="E20" t="n">
-        <v>0.287056</v>
+        <v>0.6418944999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.703</v>
+        <v>19.08</v>
       </c>
       <c r="E21" t="n">
-        <v>0.404152</v>
+        <v>0.7111440000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.063</v>
+        <v>64.252</v>
       </c>
       <c r="E22" t="n">
-        <v>0.503656</v>
+        <v>0.7601600000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -978,7 +978,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -986,16 +986,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.5</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.335604</v>
+        <v>0.3426495</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1003,7 +1003,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1011,16 +1011,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5.94</v>
+        <v>7.2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.21713175</v>
+        <v>0.218304</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1028,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.763</v>
+        <v>15.862</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6418944999999999</v>
+        <v>0.3694879166666667</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1053,7 +1053,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1061,16 +1061,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19.08</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7111440000000001</v>
+        <v>0.29277975</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1078,7 +1078,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>64.252</v>
+        <v>32.846</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7601600000000001</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.279999999999999</v>
+        <v>5.962</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3426495</v>
+        <v>0.1372</v>
       </c>
       <c r="F28" t="n">
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1136,16 +1136,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7.2</v>
+        <v>7.02</v>
       </c>
       <c r="E29" t="n">
-        <v>0.218304</v>
+        <v>0.25406925</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.862</v>
+        <v>14.22</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3694879166666667</v>
+        <v>0.3924</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>5.04</v>
       </c>
       <c r="E31" t="n">
-        <v>0.29277975</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1211,16 +1211,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>32.846</v>
+        <v>19.44</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.4396</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5.962</v>
+        <v>12.96</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1372</v>
+        <v>0.4152</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7.02</v>
+        <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>0.25406925</v>
+        <v>0.484</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.22</v>
+        <v>18.9</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3924</v>
+        <v>0.3292</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5.04</v>
+        <v>30.78</v>
       </c>
       <c r="E36" t="n">
-        <v>0.07919999999999999</v>
+        <v>0.6641999999999999</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -1336,16 +1336,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19.44</v>
+        <v>20.88</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4396</v>
+        <v>0.6058131666666667</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1353,7 +1353,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.96</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4152</v>
+        <v>0.294</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1378,7 +1378,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1389,13 +1389,13 @@
         <v>18</v>
       </c>
       <c r="E39" t="n">
-        <v>0.484</v>
+        <v>0.430208</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1403,7 +1403,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1411,16 +1411,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>18.9</v>
+        <v>63.41799999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3292</v>
+        <v>0.6138040000000001</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1428,7 +1428,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>30.78</v>
+        <v>13.5</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6641999999999999</v>
+        <v>0.3777</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -1453,7 +1453,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1461,16 +1461,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20.88</v>
+        <v>14.4</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6058131666666667</v>
+        <v>0.457056</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1478,7 +1478,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1486,16 +1486,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="E43" t="n">
-        <v>0.294</v>
+        <v>0.1872</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1503,7 +1503,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1511,16 +1511,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>18</v>
+        <v>3.6</v>
       </c>
       <c r="E44" t="n">
-        <v>0.430208</v>
+        <v>0.115104</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1528,7 +1528,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>63.41799999999999</v>
+        <v>31.14</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6138040000000001</v>
+        <v>0.552852</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1553,7 +1553,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.5</v>
+        <v>84.765</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3777</v>
+        <v>1.437724833333333</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -1578,7 +1578,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.4</v>
+        <v>19.62</v>
       </c>
       <c r="E47" t="n">
-        <v>0.457056</v>
+        <v>0.615864</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -1611,16 +1611,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7.2</v>
+        <v>14.04</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1872</v>
+        <v>0.4927665</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1636,16 +1636,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3.6</v>
+        <v>30.146</v>
       </c>
       <c r="E49" t="n">
-        <v>0.115104</v>
+        <v>0.358276</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -1653,7 +1653,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1661,16 +1661,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>31.14</v>
+        <v>17.82</v>
       </c>
       <c r="E50" t="n">
-        <v>0.552852</v>
+        <v>0.5676079999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1678,7 +1678,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>84.765</v>
+        <v>28.001</v>
       </c>
       <c r="E51" t="n">
-        <v>1.437724833333333</v>
+        <v>0.7752520000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1703,7 +1703,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1711,16 +1711,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>19.62</v>
+        <v>28.944</v>
       </c>
       <c r="E52" t="n">
-        <v>0.615864</v>
+        <v>0.6951040000000001</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.04</v>
+        <v>36.404</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4927665</v>
+        <v>1.076368</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1753,7 +1753,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>30.146</v>
+        <v>24.48</v>
       </c>
       <c r="E54" t="n">
-        <v>0.358276</v>
+        <v>0.749856</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -1778,7 +1778,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17.82</v>
+        <v>31.5</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5676079999999999</v>
+        <v>0.9526649999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1803,7 +1803,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1811,16 +1811,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>28.001</v>
+        <v>21.24</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7752520000000001</v>
+        <v>0.6369600000000001</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1828,7 +1828,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>215</v>
+        <v>270</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1836,16 +1836,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>28.944</v>
+        <v>7.92</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6951040000000001</v>
+        <v>0.2328</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1853,7 +1853,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>36.404</v>
+        <v>37.303</v>
       </c>
       <c r="E58" t="n">
-        <v>1.076368</v>
+        <v>0.9623959166666667</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -1878,7 +1878,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>24.48</v>
+        <v>43.121</v>
       </c>
       <c r="E59" t="n">
-        <v>0.749856</v>
+        <v>0.8969959166666667</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1903,7 +1903,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>31.5</v>
+        <v>9.9</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9526649999999999</v>
+        <v>0.2746837499999999</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -1928,7 +1928,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>21.24</v>
+        <v>9.9</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6369600000000001</v>
+        <v>0.2746837499999999</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7.92</v>
+        <v>13.14</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2328</v>
+        <v>0.2746837499999999</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>37.303</v>
+        <v>38.643</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9623959166666667</v>
+        <v>1.016216</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -2011,16 +2011,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>43.121</v>
+        <v>51.34299999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8969959166666667</v>
+        <v>1.498519833333333</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -2036,16 +2036,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9.9</v>
+        <v>28.303</v>
       </c>
       <c r="E65" t="n">
-        <v>0.2746837499999999</v>
+        <v>0.8117920000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -2061,16 +2061,16 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9.9</v>
+        <v>48.24</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2746837499999999</v>
+        <v>1.223259</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.14</v>
+        <v>39.686</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2746837499999999</v>
+        <v>0.7601600000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
         <v>3</v>
@@ -2103,7 +2103,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2111,16 +2111,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>38.643</v>
+        <v>37.01600000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>1.016216</v>
+        <v>0.6155040000000001</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -2128,7 +2128,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2136,16 +2136,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>51.34299999999999</v>
+        <v>23.292</v>
       </c>
       <c r="E69" t="n">
-        <v>1.498519833333333</v>
+        <v>0.287056</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2153,7 +2153,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>28.303</v>
+        <v>36.36</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8117920000000001</v>
+        <v>1.382449916666667</v>
       </c>
       <c r="F70" t="n">
         <v>4</v>
@@ -2178,7 +2178,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2186,16 +2186,16 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>48.24</v>
+        <v>35.942</v>
       </c>
       <c r="E71" t="n">
-        <v>1.223259</v>
+        <v>1.081252</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -2203,7 +2203,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>39.686</v>
+        <v>19.98</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7601600000000001</v>
+        <v>0.658944</v>
       </c>
       <c r="F72" t="n">
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2228,7 +2228,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2236,16 +2236,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>37.01600000000001</v>
+        <v>36.562</v>
       </c>
       <c r="E73" t="n">
-        <v>0.6155040000000001</v>
+        <v>1.0949275</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2253,7 +2253,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2261,16 +2261,16 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>23.292</v>
+        <v>19.08</v>
       </c>
       <c r="E74" t="n">
-        <v>0.287056</v>
+        <v>0.63489225</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2278,7 +2278,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2286,16 +2286,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>36.36</v>
+        <v>37.98</v>
       </c>
       <c r="E75" t="n">
-        <v>1.382449916666667</v>
+        <v>1.35672075</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2303,7 +2303,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>35.942</v>
+        <v>35.28</v>
       </c>
       <c r="E76" t="n">
-        <v>1.081252</v>
+        <v>0.762904</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2328,7 +2328,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2336,13 +2336,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>19.98</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>0.658944</v>
+        <v>0.4346145</v>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
         <v>2</v>
@@ -2353,7 +2353,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2361,13 +2361,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>36.562</v>
+        <v>18.72</v>
       </c>
       <c r="E78" t="n">
-        <v>1.0949275</v>
+        <v>0.7548877499999999</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>2</v>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>19.08</v>
+        <v>18.72</v>
       </c>
       <c r="E79" t="n">
-        <v>0.63489225</v>
+        <v>0.7548877499999999</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
@@ -2403,7 +2403,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>37.98</v>
+        <v>22.32</v>
       </c>
       <c r="E80" t="n">
-        <v>1.35672075</v>
+        <v>0.8699917499999998</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -2428,7 +2428,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2436,16 +2436,16 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>35.28</v>
+        <v>33.401</v>
       </c>
       <c r="E81" t="n">
-        <v>0.762904</v>
+        <v>0.7316057500000001</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2453,7 +2453,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2461,16 +2461,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>9.359999999999999</v>
+        <v>22.421</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4346145</v>
+        <v>0.5473</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2478,7 +2478,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>18.72</v>
+        <v>25.301</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7548877499999999</v>
+        <v>0.61617325</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2511,16 +2511,16 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>18.72</v>
+        <v>43.661</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7548877499999999</v>
+        <v>1.71018775</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2528,7 +2528,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>22.32</v>
+        <v>25.042</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8699917499999998</v>
+        <v>0.732608</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -2553,7 +2553,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>33.401</v>
+        <v>37.102</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7316057500000001</v>
+        <v>1.12202</v>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2578,7 +2578,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2586,16 +2586,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>22.421</v>
+        <v>18.83</v>
       </c>
       <c r="E87" t="n">
-        <v>0.5473</v>
+        <v>0.5585465000000001</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
@@ -2603,7 +2603,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>25.301</v>
+        <v>59.782</v>
       </c>
       <c r="E88" t="n">
-        <v>0.61617325</v>
+        <v>0.41460175</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
       </c>
       <c r="G88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -2628,7 +2628,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2636,16 +2636,16 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>43.661</v>
+        <v>15.581</v>
       </c>
       <c r="E89" t="n">
-        <v>1.71018775</v>
+        <v>0.6326185</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -2653,7 +2653,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2661,16 +2661,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>25.042</v>
+        <v>16.38</v>
       </c>
       <c r="E90" t="n">
-        <v>0.732608</v>
+        <v>0.4314706666666667</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
@@ -2678,7 +2678,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2686,16 +2686,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>37.102</v>
+        <v>24.84</v>
       </c>
       <c r="E91" t="n">
-        <v>1.12202</v>
+        <v>0.8031371666666667</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -2703,7 +2703,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2711,16 +2711,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>18.83</v>
+        <v>27</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5585465000000001</v>
+        <v>1.2948435</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>59.782</v>
+        <v>25.481</v>
       </c>
       <c r="E93" t="n">
-        <v>0.41460175</v>
+        <v>0.735132</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2761,16 +2761,16 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>15.581</v>
+        <v>28.721</v>
       </c>
       <c r="E94" t="n">
-        <v>0.6326185</v>
+        <v>0.9289224999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2784,7 +2784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2816,7 +2816,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -2835,7 +2835,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2880,7 +2880,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
         <v>10</v>
@@ -2888,31 +2888,31 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
@@ -2920,18 +2920,18 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2939,15 +2939,15 @@
         <v>12</v>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -2955,23 +2955,23 @@
         <v>13</v>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -2979,28 +2979,28 @@
         <v>16</v>
       </c>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" t="n">
         <v>17</v>
-      </c>
-      <c r="B25" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B27" t="n">
         <v>20</v>
@@ -3008,135 +3008,135 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" t="n">
         <v>18</v>
-      </c>
-      <c r="B28" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" t="n">
         <v>21</v>
-      </c>
-      <c r="B31" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B40" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B44" t="n">
         <v>33</v>
@@ -3168,7 +3168,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" t="n">
         <v>37</v>
@@ -3179,31 +3179,31 @@
         <v>37</v>
       </c>
       <c r="B49" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B50" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B51" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53">
@@ -3211,7 +3211,7 @@
         <v>40</v>
       </c>
       <c r="B53" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54">
@@ -3219,39 +3219,39 @@
         <v>40</v>
       </c>
       <c r="B54" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B55" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B56" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
+        <v>42</v>
+      </c>
+      <c r="B57" t="n">
         <v>44</v>
-      </c>
-      <c r="B57" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B58" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
@@ -3259,71 +3259,71 @@
         <v>45</v>
       </c>
       <c r="B59" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B60" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B61" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B62" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B63" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B64" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B65" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B66" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B67" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68">
@@ -3331,92 +3331,92 @@
         <v>54</v>
       </c>
       <c r="B68" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B69" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B70" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B71" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B72" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B73" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B74" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B75" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B76" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B77" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B78" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B79" t="n">
         <v>66</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B81" t="n">
         <v>68</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B82" t="n">
         <v>69</v>
@@ -3448,26 +3448,26 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B83" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B84" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B85" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86">
@@ -3475,60 +3475,60 @@
         <v>71</v>
       </c>
       <c r="B86" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B87" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B88" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B89" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B90" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B91" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B92" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B93" t="n">
         <v>79</v>
@@ -3547,36 +3547,36 @@
         <v>80</v>
       </c>
       <c r="B95" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
+        <v>80</v>
+      </c>
+      <c r="B96" t="n">
         <v>81</v>
-      </c>
-      <c r="B96" t="n">
-        <v>82</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
+        <v>81</v>
+      </c>
+      <c r="B97" t="n">
         <v>82</v>
-      </c>
-      <c r="B97" t="n">
-        <v>83</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
+        <v>82</v>
+      </c>
+      <c r="B98" t="n">
         <v>83</v>
-      </c>
-      <c r="B98" t="n">
-        <v>87</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B99" t="n">
         <v>84</v>
@@ -3595,62 +3595,54 @@
         <v>85</v>
       </c>
       <c r="B101" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B102" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B103" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B104" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B105" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B106" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B107" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>91</v>
-      </c>
-      <c r="B108" t="n">
         <v>92</v>
       </c>
     </row>
